--- a/reports/Debug-snowbowl-20251230/For The Week Ending (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Week Ending (Prior Year)_Payroll_history.xlsx
@@ -19,6 +19,9 @@
     <t>department</t>
   </si>
   <si>
+    <t>D8030</t>
+  </si>
+  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -34,7 +37,64 @@
     <t>D7010</t>
   </si>
   <si>
-    <t>D8030</t>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D6721</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>D6781</t>
   </si>
   <si>
     <t>D2000</t>
@@ -47,66 +107,6 @@
   </si>
   <si>
     <t>D8020</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>D6781</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D6721</t>
-  </si>
-  <si>
-    <t>D6790</t>
   </si>
   <si>
     <t>D1100</t>
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>1794.54</v>
+        <v>1648.36</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -521,7 +521,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>614.17</v>
+        <v>1794.54</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -529,7 +529,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>417.16</v>
+        <v>614.17</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -537,7 +537,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>1777.38</v>
+        <v>417.16</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -545,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>1182.97</v>
+        <v>1777.38</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -553,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>1648.36</v>
+        <v>1182.97</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -561,7 +561,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>14127.24</v>
+        <v>5478.58</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -569,7 +569,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>635.48</v>
+        <v>5372.76</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -577,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>1862.08</v>
+        <v>775.42</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>1678.63</v>
+        <v>417.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -593,7 +593,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>5478.58</v>
+        <v>1268.50</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -601,7 +601,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>5372.76</v>
+        <v>2297.45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -609,7 +609,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>775.42</v>
+        <v>1205.24</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -617,7 +617,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>417.16</v>
+        <v>1914.80</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>1268.50</v>
+        <v>12364.61</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -633,7 +633,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>2297.45</v>
+        <v>4933.80</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -641,7 +641,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>1205.24</v>
+        <v>1585.00</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -649,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>1914.80</v>
+        <v>1400.38</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -721,7 +721,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>12364.61</v>
+        <v>14127.24</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -729,7 +729,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>4933.80</v>
+        <v>635.48</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -737,7 +737,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>1585.00</v>
+        <v>1862.08</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -745,7 +745,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>1400.38</v>
+        <v>1678.63</v>
       </c>
     </row>
     <row r="32" spans="1:2">
